--- a/EXCEL.xlsx
+++ b/EXCEL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ram/Library/Mobile Documents/com~apple~CloudDocs/Shared/GitHub Repos/SDB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA95606-65FD-3D4B-9A48-7FA4DA6B3707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7251781-8E8F-9040-919D-467F1CF4F919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-51020" yWindow="-540" windowWidth="51200" windowHeight="26400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-51200" yWindow="-540" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="External Connections" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="234">
   <si>
     <t>#</t>
   </si>
@@ -623,65 +623,128 @@
     <t>Domain is with namescheap, not cloudflare. Is this a problem?</t>
   </si>
   <si>
-    <t>P0</t>
-  </si>
-  <si>
-    <t>P1</t>
-  </si>
-  <si>
-    <t>P2</t>
-  </si>
-  <si>
-    <t>P3</t>
-  </si>
-  <si>
-    <t>P5</t>
-  </si>
-  <si>
-    <t>P7</t>
-  </si>
-  <si>
-    <t>P8</t>
-  </si>
-  <si>
-    <t>P9</t>
-  </si>
-  <si>
-    <t>P4A</t>
-  </si>
-  <si>
-    <t>P4B</t>
-  </si>
-  <si>
-    <t>P6A</t>
-  </si>
-  <si>
-    <t>P6B</t>
-  </si>
-  <si>
-    <t>Implement</t>
-  </si>
-  <si>
-    <t>Test</t>
-  </si>
-  <si>
-    <t>Codebase</t>
-  </si>
-  <si>
     <t>v1.CmQKHHN0YXRpY2tleS1lMDBrMXZmcmp0czhoNHBmOXoSIXNlcnZpY2VhY2NvdW50LWUwMG55ZG1xMmMwYzE3ZGVrYTIMCLWV380GEI_FiowBOgwItJj3mAcQwNH8kQNAAloDZTAw.AAAAAAAAAAHMCPXEm5QeCtzs6HAC-yuqc8Vr-l6edmicL_8UcJSnVTYxCTtk_x6z_srzRrjZyHA2QOPvpIm1iBm4prxFhB4A</t>
   </si>
   <si>
     <t>v1.CmMKHHN0YXRpY2tleS1lMDBlYWR2MmF0eHd0emM1YTISIXNlcnZpY2VhY2NvdW50LWUwMGg3cTB3ZGVyNDZhMnMwcDIMCP2V380GEJSomP0BOgsI_Zj3mAcQgJ7vK0ACWgNlMDA.AAAAAAAAAAF5XKm7O_vjpc4npzkREDNBYox4BXKwyVN-75O-sTLIBnKwCRm4uo9dL2D0UdoC558-ZLb3dwK5onX_slSfL5wL</t>
+  </si>
+  <si>
+    <t>1Password</t>
+  </si>
+  <si>
+    <t>no staging URL. Only local host</t>
+  </si>
+  <si>
+    <t>+14155238886</t>
+  </si>
+  <si>
+    <t>git config --global --add safe.directory /opt/edupod/app &amp;&amp; git pull &amp;&amp; pnpm build</t>
+  </si>
+  <si>
+    <t>teacher@alnoor.test</t>
+  </si>
+  <si>
+    <t>owner@mdad.test</t>
+  </si>
+  <si>
+    <t>parent@mdad.test</t>
+  </si>
+  <si>
+    <t>92xH4sid</t>
+  </si>
+  <si>
+    <t>Password123!</t>
+  </si>
+  <si>
+    <t>admin@edupod.app</t>
+  </si>
+  <si>
+    <t>owner@alnoor.test</t>
+  </si>
+  <si>
+    <t>admin@alnoor.test</t>
+  </si>
+  <si>
+    <t>parent@alnoor.test</t>
+  </si>
+  <si>
+    <t>owner@cedar.test</t>
+  </si>
+  <si>
+    <t>admin@cedar.test</t>
+  </si>
+  <si>
+    <t>teacher@cedar.test</t>
+  </si>
+  <si>
+    <t>parent@cedar.test</t>
+  </si>
+  <si>
+    <t>owner@nhqs.test</t>
+  </si>
+  <si>
+    <t>admin@nhqs.test</t>
+  </si>
+  <si>
+    <t>teacher@nhqs.test</t>
+  </si>
+  <si>
+    <t>parent@nhqs.test</t>
+  </si>
+  <si>
+    <t>admin@mdad.test</t>
+  </si>
+  <si>
+    <t>teacher@mdad.test</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>School</t>
+  </si>
+  <si>
+    <t>Platform Admin</t>
+  </si>
+  <si>
+    <t>School Owner</t>
+  </si>
+  <si>
+    <t>School Admin</t>
+  </si>
+  <si>
+    <t>Teacher</t>
+  </si>
+  <si>
+    <t>Parent</t>
+  </si>
+  <si>
+    <t>Al Noor Academy</t>
+  </si>
+  <si>
+    <t>Cedar International</t>
+  </si>
+  <si>
+    <t>Nurul Huda School</t>
+  </si>
+  <si>
+    <t>Midaad Ul Qalam</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$$-409]#,##0"/>
-  </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -740,8 +803,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -767,6 +843,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -814,18 +896,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -837,9 +913,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -849,20 +922,39 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1167,18 +1259,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5" style="3" customWidth="1"/>
-    <col min="2" max="2" width="34" style="3" customWidth="1"/>
-    <col min="3" max="3" width="30" style="3" customWidth="1"/>
-    <col min="4" max="4" width="55" style="3" customWidth="1"/>
-    <col min="5" max="5" width="60" style="3" customWidth="1"/>
-    <col min="6" max="16384" width="8.83203125" style="3"/>
+    <col min="1" max="1" width="5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="34" style="2" customWidth="1"/>
+    <col min="3" max="3" width="30" style="2" customWidth="1"/>
+    <col min="4" max="4" width="55" style="2" customWidth="1"/>
+    <col min="5" max="5" width="60" style="2" customWidth="1"/>
+    <col min="6" max="6" width="42.33203125" style="12" customWidth="1"/>
+    <col min="7" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="28" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1195,839 +1288,856 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A3" s="5">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+    </row>
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+    <row r="4" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="5">
+      <c r="F4" s="12" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
+    <row r="7" spans="1:11" ht="112" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
+      <c r="F7" s="12" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
+    <row r="9" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="7" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
+      <c r="K9" s="16" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
+    <row r="11" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
+    <row r="12" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-    </row>
-    <row r="14" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+    </row>
+    <row r="14" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A14" s="3">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="5" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
+    <row r="15" spans="1:11" ht="30" x14ac:dyDescent="0.2">
+      <c r="A15" s="3">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="45" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
+    <row r="16" spans="1:11" ht="45" x14ac:dyDescent="0.2">
+      <c r="A16" s="3">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="12" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
     </row>
     <row r="18" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
+      <c r="A18" s="3">
         <v>14</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="5" t="s">
         <v>62</v>
       </c>
+      <c r="F18" s="12" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="19" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
+      <c r="A19" s="3">
         <v>15</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="3" t="s">
-        <v>192</v>
+      <c r="F19" s="12" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
+      <c r="A20" s="3">
         <v>16</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="7" t="s">
+      <c r="D20" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="13" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
+    <row r="21" spans="1:6" ht="32" x14ac:dyDescent="0.2">
+      <c r="A21" s="3">
         <v>17</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="D21" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="12" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="3">
         <v>18</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D22" s="7" t="s">
+      <c r="D22" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="5" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
+      <c r="F22" s="12" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="3">
         <v>19</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="5" t="s">
         <v>82</v>
       </c>
+      <c r="F23" s="12" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
+      <c r="A24" s="3">
         <v>20</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="7" t="s">
+      <c r="D24" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="5" t="s">
         <v>86</v>
       </c>
+      <c r="F24" s="14" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="25" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
+      <c r="A25" s="3">
         <v>21</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="C25" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="D25" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="F25" s="15"/>
     </row>
     <row r="26" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A26" s="5">
+      <c r="A26" s="3">
         <v>22</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C26" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="7" t="s">
+      <c r="D26" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>94</v>
       </c>
+      <c r="F26" s="15"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
     </row>
     <row r="28" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A28" s="5">
+      <c r="A28" s="3">
         <v>23</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C28" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A29" s="5">
+      <c r="A29" s="3">
         <v>24</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="C29" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D29" s="7" t="s">
+      <c r="D29" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="E29" s="7" t="s">
+      <c r="E29" s="5" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A30" s="5">
+      <c r="A30" s="3">
         <v>25</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="7" t="s">
+      <c r="C30" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D30" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="7" t="s">
+      <c r="E30" s="5" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="30" x14ac:dyDescent="0.2">
-      <c r="A31" s="5">
+      <c r="A31" s="3">
         <v>26</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C31" s="7" t="s">
+      <c r="C31" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="5" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="5">
+      <c r="A32" s="3">
         <v>27</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C32" s="7" t="s">
+      <c r="C32" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="7" t="s">
+      <c r="D32" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="5" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A33" s="5">
+      <c r="A33" s="3">
         <v>28</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="5" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A34" s="5">
+      <c r="A34" s="3">
         <v>29</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="E34" s="7" t="s">
+      <c r="E34" s="5" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A35" s="5">
+      <c r="A35" s="3">
         <v>30</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="5" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A36" s="5">
+      <c r="A36" s="3">
         <v>31</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C36" s="7" t="s">
+      <c r="C36" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="5" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A37" s="5">
+      <c r="A37" s="3">
         <v>32</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C37" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="D37" s="7" t="s">
+      <c r="D37" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="5" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A38" s="5">
+      <c r="A38" s="3">
         <v>33</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="D38" s="7" t="s">
+      <c r="D38" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="5" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A39" s="5">
+      <c r="A39" s="3">
         <v>34</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D39" s="7" t="s">
+      <c r="D39" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="5" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A40" s="5">
+      <c r="A40" s="3">
         <v>35</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C40" s="7" t="s">
+      <c r="C40" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="D40" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A41" s="5">
+      <c r="A41" s="3">
         <v>36</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C41" s="7" t="s">
+      <c r="C41" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="D41" s="7" t="s">
+      <c r="D41" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="5">
+      <c r="A42" s="3">
         <v>37</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="D42" s="7" t="s">
+      <c r="D42" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A43" s="5">
+      <c r="A43" s="3">
         <v>38</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="5" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A44" s="5">
+      <c r="A44" s="3">
         <v>39</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C44" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="D44" s="7" t="s">
+      <c r="D44" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A45" s="5">
+      <c r="A45" s="3">
         <v>40</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C45" s="7" t="s">
+      <c r="C45" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="D45" s="7" t="s">
+      <c r="D45" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A46" s="5">
+      <c r="A46" s="3">
         <v>41</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="D46" s="7" t="s">
+      <c r="D46" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E46" s="7" t="s">
+      <c r="E46" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A47" s="5">
+      <c r="A47" s="3">
         <v>42</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="C47" s="7" t="s">
+      <c r="C47" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="D47" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="E47" s="7" t="s">
+      <c r="E47" s="5" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="5">
+      <c r="A48" s="3">
         <v>43</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="C48" s="7" t="s">
+      <c r="C48" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D48" s="7" t="s">
+      <c r="D48" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="E48" s="7" t="s">
+      <c r="E48" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="5">
+      <c r="A49" s="3">
         <v>44</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="7" t="s">
+      <c r="C49" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="D49" s="7" t="s">
+      <c r="D49" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="E49" s="7" t="s">
+      <c r="E49" s="5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="5">
+      <c r="A50" s="3">
         <v>45</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="C50" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D50" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="E50" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="30" x14ac:dyDescent="0.2">
-      <c r="A51" s="5">
+      <c r="A51" s="3">
         <v>46</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C51" s="7" t="s">
+      <c r="C51" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="D51" s="7" t="s">
+      <c r="D51" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="E51" s="5" t="s">
         <v>191</v>
       </c>
     </row>
@@ -2048,144 +2158,291 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF84398B-CD2E-4D40-AF57-24EA031466F6}">
-  <dimension ref="B2:E15"/>
+  <dimension ref="E3:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="11"/>
-    <col min="2" max="2" width="6.33203125" style="11" customWidth="1"/>
-    <col min="3" max="4" width="10.83203125" style="11"/>
-    <col min="5" max="5" width="10.83203125" style="15"/>
-    <col min="6" max="16384" width="10.83203125" style="11"/>
+    <col min="1" max="4" width="10.83203125" style="8"/>
+    <col min="5" max="5" width="10.83203125" style="9"/>
+    <col min="6" max="6" width="18.5" style="8" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" style="8" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="8"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="E2" s="15" t="s">
+    <row r="3" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F3" s="19" t="s">
+        <v>220</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="4" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F4" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>204</v>
+      </c>
+      <c r="H4" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F5" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F6" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H6" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="7" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F7" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="8" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F8" s="18" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="C3" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B4" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="C4" s="14">
-        <v>20</v>
-      </c>
-      <c r="D4" s="14">
-        <v>6</v>
-      </c>
-      <c r="E4" s="16"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B5" s="13" t="s">
-        <v>196</v>
-      </c>
-      <c r="C5" s="14">
-        <v>36</v>
-      </c>
-      <c r="D5" s="14">
-        <v>10</v>
-      </c>
-      <c r="E5" s="16">
-        <f>17643-369</f>
-        <v>17274</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B6" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="14">
-        <v>27</v>
-      </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="16">
-        <f>18232-182</f>
-        <v>18050</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B7" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="16"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B8" s="13" t="s">
+      <c r="G8" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H8" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F9" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H9" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="10" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F10" s="18" t="s">
+        <v>211</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="11" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F11" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F12" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H12" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="13" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F13" s="18" t="s">
+        <v>214</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="14" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F14" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="15" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F15" s="18" t="s">
+        <v>216</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="16" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F16" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="17" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F17" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H17" s="17" t="s">
+        <v>225</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="18" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F18" s="18" t="s">
+        <v>218</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="19" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F19" s="18" t="s">
+        <v>219</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="6:9" x14ac:dyDescent="0.2">
+      <c r="F20" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B9" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B10" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="16"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B11" s="13" t="s">
+      <c r="G20" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="16"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B12" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="16"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B13" s="13" t="s">
-        <v>200</v>
-      </c>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="16"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B14" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="16"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B15" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="16"/>
+      <c r="H20" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>232</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="F4" r:id="rId1" xr:uid="{49B2382D-6215-9440-A8D9-7CF6D7EC03A4}"/>
+    <hyperlink ref="F5" r:id="rId2" xr:uid="{112B83F0-F770-B547-BB6F-BA17E07D4A7C}"/>
+    <hyperlink ref="F6" r:id="rId3" xr:uid="{9A848902-70EF-5F4B-8DDD-149FE727C4E9}"/>
+    <hyperlink ref="F7" r:id="rId4" xr:uid="{FAA52B0D-B527-DE44-BD10-4E420F21A9DB}"/>
+    <hyperlink ref="F10" r:id="rId5" xr:uid="{EE6D3AFD-83C7-0B4C-AAE3-3A43FB7F9C82}"/>
+    <hyperlink ref="F11" r:id="rId6" xr:uid="{7FC236C7-9D88-3A4D-AAA9-4CC5537D2F6D}"/>
+    <hyperlink ref="F12" r:id="rId7" xr:uid="{46AC0C43-2B87-9940-98D8-F57B64798176}"/>
+    <hyperlink ref="F13" r:id="rId8" xr:uid="{0330A7BF-9C7A-8049-9B3F-0EA37914D3B9}"/>
+    <hyperlink ref="F14" r:id="rId9" xr:uid="{BB0BE67E-86A2-8441-A564-AD768EC8F0BE}"/>
+    <hyperlink ref="F15" r:id="rId10" xr:uid="{CA3D3E1A-97AB-F940-9108-651642B23D94}"/>
+    <hyperlink ref="F16" r:id="rId11" xr:uid="{3EF0882F-861C-194A-B9DB-7CF9701380EA}"/>
+    <hyperlink ref="F17" r:id="rId12" xr:uid="{BFB0E4B8-5559-D640-84AB-68D821F360A3}"/>
+    <hyperlink ref="F18" r:id="rId13" xr:uid="{68E1CF0E-ADA3-B648-A8BE-FB53DA0F4167}"/>
+    <hyperlink ref="F19" r:id="rId14" xr:uid="{27F1FDA8-B45E-DC47-B505-DFDB87AB9C7B}"/>
+    <hyperlink ref="F20" r:id="rId15" xr:uid="{E31F64A2-B69B-4549-9E00-A7A4746195D2}"/>
+    <hyperlink ref="F8" r:id="rId16" xr:uid="{5919BFFF-F49D-5346-828F-53D628F4E6C7}"/>
+    <hyperlink ref="F9" r:id="rId17" xr:uid="{3932621C-1E2A-054F-B980-B628202CD677}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>